--- a/medford_svetilniki_khirurgicheskie.xlsx
+++ b/medford_svetilniki_khirurgicheskie.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Светильники хирургические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray — всего 20 позиций.</t>
+          <t>Светильники хирургические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_svetilniki_khirurgicheskie.xlsx
+++ b/medford_svetilniki_khirurgicheskie.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать светильники хирургические для клиники?</t>
+          <t>Какая освещённость нужна для операционной?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Тип ? Предлагаем указанную область применения, но вы можете использовать товар по вашему усмотрению, Конструкция, Освещенность, кЛк, Индекс цветопередачи (Ra)). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Зависит от типа вмешательств. Для поверхностных манипуляций и осмотров достаточно меньших значений освещённости, для глубоких полостных операций выбирают модели ближе к 160 кЛк. В каталоге освещённость составляет от 50 до 160 кЛк. Ориентируются на профиль операций учреждения, а не на максимальную цифру характеристики.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Что означает индекс цветопередачи Ra?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Ra показывает, насколько точно светильник передаёт естественные цвета освещаемых тканей. Для хирургии его значение должно быть выше 90, а лучше выше 95, чтобы врач различал мельчайшие оттенки. В каталоге Ra моделей — 95–99, максимум дают светильники KLS Martin MarLED (Ra 99) и FotonFly (Ra 98).</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Чем однокупольный светильник отличается от двухкупольного?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Mindray. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Однокупольный светильник даёт прямой поток света из одной головки. Двухкупольные модели (KLS Martin MarLED V16/V10, TriLite S600) имеют две головки и освещают поле под разными углами, что сильнее подавляет тени при сложных операциях. Выбор зависит от характера вмешательств и требований к бестеневому освещению.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Потолочный или передвижной светильник выбрать?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Потолочные модели стационарны, дают стабильное положение и освобождают пол операционной, но требуют монтажа на потолок. Передвижные перемещаются между кабинетами и подходят там, где стационарная установка невозможна. Настенные экономят место. Выбор определяется планировкой помещения и тем, нужна ли мобильность светильника.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Что такое режим ЭНДО?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Режим ЭНДО — сниженная яркость и настройка света для эндоскопических этапов операции, когда яркое освещение мешает восприятию изображения с монитора. Этот режим есть у ряда моделей каталога, например Mindray HyLED X9, 9600M и МЕДИН СМХ-Е1. Наличие режима ЭНДО уточняют по спецификации конкретной модели.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Как называется лампа в хирургии?</t>
+          <t>Нагревается ли операционное поле под светильником?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Современные светодиодные светильники практически не нагревают операционное поле, в отличие от галогенных и газоразрядных ламп. Все модели каталога — светодиодные. Это снижает подсыхание тканей и тепловую нагрузку на хирурга и пациента при длительных вмешательствах, а также продлевает срок службы источника света.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Как работает хирургическая бестеневая лампа?</t>
+          <t>Можно ли стерилизовать рукоятку управления?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>У многих хирургических светильников центральная рукоятка снимается и автоклавируется, что позволяет хирургу регулировать положение светильника, не нарушая стерильности. Наличие снимаемой стерилизуемой рукоятки и способ её обработки уточняют по документации конкретной модели, поскольку исполнение отличается у разных производителей.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли регистрационное удостоверение?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Да. Хирургический светильник — медицинское изделие, вводимое в оборот при действующем регистрационном удостоверении Росздравнадзора на модель. Перед приобретением сверяют статус РУ, требования к электропитанию, при необходимости наличие аварийного блока и условия сервисного обслуживания у поставщика.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>svetilniki_khirurgicheskie</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Светильники хирургические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray.</t>
+          <t>Светильники хирургические создают яркое, равномерное и направленное освещение операционного поля с минимумом теней от рук и инструментов. В каталоге собраны потолочные, передвижные и настенные модели Mindray HyLED, KLS Martin MarLED, TriLite, FotonFly, ЭМАЛЕД, Аксима и МЕДИН с освещённостью от 50 до 160 кЛк. Индекс цветопередачи (Ra) моделей — 95–99, цветовая температура — в диапазоне 3000–5100 К, глубина освещения на уровне 20% — от 490 до 1500 мм. Часть моделей имеет режим ЭНДО для работы при эндоскопических вмешательствах.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Классификация хирургических светильников</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое светильники хирургические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4694,239 +4732,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Классификация хирургических светильников</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Признак</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Тип ? Предлагаем указанную область применения, но вы можете использовать товар по вашему усмотрению</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Конструкция</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Освещенность, кЛк</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Индекс цветопередачи (Ra)</t>
+          <t>Варианты</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Хирургический светильник Mindray HyLED X9</t>
+          <t>По типу установки</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Потолочный</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Однокупольная</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>97</t>
+          <t>потолочные / передвижные / настенные</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Светильник Mindray HyLED 9300M (передвижной)</t>
+          <t>По числу куполов</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Передвижной</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Однокупольная</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>96</t>
+          <t>однокупольные / двух- и многокупольные</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Светильник Mindray HyLED 9600M (передвижной)</t>
+          <t>По источнику света</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Передвижной</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Однокупольная</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>96</t>
+          <t>светодиодные (LED) / галогенные и газоразрядные</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Светильник операционный TriLite LED серии S600</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Потолочный</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Двухкупольная Однокупольная</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>120 160</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Медицинский хирургический светильник FotonFly 5MW</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Настенный</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Однокупольная</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Светильник операционный TriLite серии LS800</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Потолочный</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Однокупольная</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>120 160</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>95</t>
+          <t>По режиму ЭНДО</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>с режимом ЭНДО / без него</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4938,7 +4820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5264,12 +5146,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите тип крепления</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается светильники хирургические: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала выбирают исполнение под помещение: потолочные модели (Mindray HyLED X9, МЕДИН СМХ-Е1) стационарны и освобождают пол, передвижные (ЭМАЛЕД 200П, Аксима СД 160М, KLS Martin E1) перемещаются между кабинетами, настенные (FotonFly 5MW) экономят место. Тип крепления зависит от планировки операционной и возможности монтажа на потолок.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5309,12 +5191,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Подберите освещённость под операции</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Освещённость моделей каталога — от 50 до 160 кЛк. Для поверхностных манипуляций и осмотров достаточно меньших значений, для глубоких полостных операций выбирают модели ближе к 160 кЛк (Mindray HyLED X9, Аксима СД 160М, МЕДИН СМХ-Е1). Требуемый уровень определяют по профилю вмешательств учреждения, а не по максимуму характеристики.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5354,12 +5236,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Проверьте цветопередачу и температуру</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Тип ? Предлагаем указанную область применения, но вы можете использовать товар по вашему усмотрению, Конструкция, Освещенность, кЛк, Индекс цветопередачи (Ra). Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Индекс цветопередачи Ra у моделей — 95–99; чем выше, тем точнее хирург различает оттенки тканей. Максимум дают KLS Martin MarLED (Ra 99) и FotonFly (Ra 98). Цветовая температура в каталоге — 3000–5100 К, оптимальный диапазон близок к дневному свету. Часть моделей позволяет регулировать температуру под этап операции.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5399,12 +5281,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените глубину освещения и число куполов</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Mindray.</t>
+          <t>Глубина освещения на уровне 20% показывает, насколько глубоко в рану проникает качественный свет; в каталоге — от 490 до 1500 мм. Однокупольные светильники дают прямой поток, двухкупольные (KLS Martin MarLED V16/V10, TriLite S600) освещают поле под разными углами и лучше подавляют тени при сложных вмешательствах.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5444,12 +5326,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Учтите режим ЭНДО и управление</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Для эндоскопических этапов важен режим ЭНДО с приглушённым светом — он есть у Mindray HyLED X9, 9600M, МЕДИН СМХ-Е1 и ряда других. Управление яркостью и температурой выносят на сенсорную панель, а стерильную рукоятку делают снимаемой и автоклавируемой. Наличие этих функций уточняют по спецификации модели.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5489,12 +5371,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните питание и регистрацию</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Проверяют требования к электропитанию и, при необходимости, наличие блока аварийного питания для операционной. Перед вводом в оборот сверяют действующее регистрационное удостоверение Росздравнадзора на модель и условия сервисной поддержки. LED-светильники служат дольше галогенных, но ресурс диодов и доступность запчастей уточняют у поставщика.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5544,7 +5426,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Светильники хирургические подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Mindray. При выборе обращают внимание на тип ? предлагаем указанную область применения, конструкция, освещенность, индекс цветопередачи (ra), а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Хирургический светильник оценивают не по одной яркости, а по связке параметров. Освещённость подбирают под характер операций: для поверхностных манипуляций хватает меньших значений, для глубоких полостных нужны модели ближе к 160 кЛк с большой глубиной освещения. Ra ниже 95 я не рассматриваю — от цветопередачи зависит, насколько верно хирург различает ткани. Отдельно смотрю на тип крепления под конкретное помещение и на снимаемую автоклавируемую рукоятку.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5828,13 +5710,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое светильники хирургические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Светильники хирургические — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Mindray. Подберём вариант под задачи вашего отделения.</t>
+          <t>Хирургический светильник обеспечивает бестеневое освещение операционного поля с минимумом теней от рук и инструментов. Ключевые параметры — освещённость (в каталоге 50–160 кЛк), индекс цветопередачи Ra (95–99), цветовая температура (3000–5100 К) и глубина освещения. По типу установки светильники делят на потолочные, передвижные и настенные, по числу куполов — на одно- и двухкупольные. Современные модели светодиодные и почти не нагревают поле. Освещённость выбирают под тип вмешательств: меньшую — для осмотров и малых манипуляций, максимальную — для глубоких полостных операций.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5871,13 +5753,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое хирургический светильник</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Тип ? Предлагаем указанную область применения, но вы можете использовать товар по вашему усмотрению, Конструкция, Освещенность, кЛк, Индекс цветопередачи (Ra)), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Хирургический (операционный) светильник — оборудование для яркого равномерного освещения операционного поля с подавлением теней от рук, инструментов и головы хирурга. Осветительная головка содержит светодиоды и оптическую систему из линз, зеркал и диффузоров. Современные LED-модели почти не нагревают поле и позволяют регулировать яркость и цветовую температуру.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5914,13 +5796,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Ключевые характеристики</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Основные параметры — освещённость (в каталоге 50–160 кЛк), индекс цветопередачи Ra (95–99), цветовая температура (3000–5100 К) и глубина освещения на уровне 20% (490–1500 мм). Освещённость подбирают под тип операций, Ra отвечает за точность различения тканей, глубина освещения — за качество света в глубине раны.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5957,13 +5839,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Виды хирургических светильников</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>По типу установки светильники делят на потолочные, передвижные и настенные; по числу куполов — на одно- и двухкупольные; по источнику света — на светодиодные, галогенные и газоразрядные. В каталоге представлены преимущественно светодиодные модели Mindray HyLED, KLS Martin MarLED, TriLite, FotonFly, ЭМАЛЕД, Аксима и МЕДИН в потолочном и передвижном исполнении.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5980,6 +5862,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Как выбрать светильник</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Выбор начинают с типа крепления под помещение, затем подбирают освещённость под характер вмешательств и проверяют Ra, цветовую температуру и глубину освещения. Для эндоскопических этапов важен режим ЭНДО, для сложных операций — двухкупольная схема. Дополнительно оценивают снимаемую автоклавируемую рукоятку, требования к питанию и наличие регистрационного удостоверения.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>svetilniki_khirurgicheskie</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
